--- a/KatalonData/VVTApiIVT/VVTApiIVT_Login.xlsx
+++ b/KatalonData/VVTApiIVT/VVTApiIVT_Login.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\VVTApiIVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2C185E-9A0C-4E10-95C9-8F880BEC944E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{03FE59E4-E39F-4243-9F4B-EED4190D4468}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="SubmitRequest" sheetId="1" r:id="rId1"/>
+    <sheet name="SubmitRequest" r:id="rId1" sheetId="1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>Result</t>
   </si>
@@ -65,16 +65,22 @@
     <t>Submit Request:
 applicationId- will always be 975.
 remittanceId- will always be unique(alphanumeric).</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Mon May 25 13:11:58 IST 2026</t>
   </si>
   <si>
     <t>{
   "amount": 20.00,
   "clientAccountNumber": "123456",
   "applicationId": "975",
-  "remittanceId": "bbg12357",
+  "remittanceId": "bbg12359",
   "pinpadName": "Counter-001",
   "parcel": [
-    ["1", "2", "4"],
+    ["Ref785", "5", "10.50"],
     ["1", "2", "3"],
     ["1", "2", "3"]
   ],
@@ -105,11 +111,27 @@
   }
 }</t>
   </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Mon May 25 13:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 14:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 14:36:21 IST 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -182,37 +204,40 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -229,10 +254,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -267,7 +292,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -319,7 +344,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -430,21 +455,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -461,7 +486,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -533,92 +558,90 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="16.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="7" style="4" width="8.7265625" collapsed="true"/>
+    <col min="8" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2" s="4" t="s">
+    <row customFormat="1" ht="409.5" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>9</v>
+      <c r="F2" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-      <c r="B6"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7"/>
-      <c r="B7"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-      <c r="B8"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9"/>
-      <c r="B9"/>
+      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/VVTApiIVT/VVTApiIVT_Login.xlsx
+++ b/KatalonData/VVTApiIVT/VVTApiIVT_Login.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>Result</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Mon May 25 14:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 28 18:18:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -604,7 +607,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
